--- a/ml_api/diabetes_modificado.xlsx
+++ b/ml_api/diabetes_modificado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrah\OneDrive\Escritorio\GitHub\WebPrediccionDT2\ml_api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFBB67F-3A67-4DCA-89B1-4148428F6870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1997F74C-7311-4022-91CB-E315D4AA3F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -77,6 +77,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -108,12 +114,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5523,61 +5530,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A177">
-        <v>0</v>
-      </c>
-      <c r="B177">
+    <row r="177" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
+        <v>0</v>
+      </c>
+      <c r="B177" s="2">
         <v>104</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="2">
         <v>76</v>
       </c>
-      <c r="D177">
-        <v>20.536458333333329</v>
-      </c>
-      <c r="E177">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F177">
+      <c r="D177" s="2">
+        <v>20.536458333333329</v>
+      </c>
+      <c r="E177" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F177" s="2">
         <v>18.399999999999999</v>
       </c>
-      <c r="G177">
+      <c r="G177" s="2">
         <v>0.58199999999999996</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="2">
         <v>27</v>
       </c>
-      <c r="I177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A178">
-        <v>1</v>
-      </c>
-      <c r="B178">
+      <c r="I177" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <v>1</v>
+      </c>
+      <c r="B178" s="2">
         <v>91</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="2">
         <v>64</v>
       </c>
-      <c r="D178">
+      <c r="D178" s="2">
         <v>24</v>
       </c>
-      <c r="E178">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F178">
+      <c r="E178" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F178" s="2">
         <v>29.2</v>
       </c>
-      <c r="G178">
+      <c r="G178" s="2">
         <v>0.192</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="2">
         <v>21</v>
       </c>
-      <c r="I178">
+      <c r="I178" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5610,61 +5617,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A180">
+    <row r="180" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="2">
         <v>2</v>
       </c>
-      <c r="B180">
+      <c r="B180" s="2">
         <v>146</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="2">
         <v>76</v>
       </c>
-      <c r="D180">
+      <c r="D180" s="2">
         <v>35</v>
       </c>
-      <c r="E180">
+      <c r="E180" s="2">
         <v>194</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="2">
         <v>38.200000000000003</v>
       </c>
-      <c r="G180">
+      <c r="G180" s="2">
         <v>0.32900000000000001</v>
       </c>
-      <c r="H180">
+      <c r="H180" s="2">
         <v>29</v>
       </c>
-      <c r="I180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A181">
+      <c r="I180" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="2">
         <v>9</v>
       </c>
-      <c r="B181">
+      <c r="B181" s="2">
         <v>184</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="2">
         <v>85</v>
       </c>
-      <c r="D181">
+      <c r="D181" s="2">
         <v>15</v>
       </c>
-      <c r="E181">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F181">
+      <c r="E181" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F181" s="2">
         <v>30</v>
       </c>
-      <c r="G181">
+      <c r="G181" s="2">
         <v>1.2130000000000001</v>
       </c>
-      <c r="H181">
+      <c r="H181" s="2">
         <v>49</v>
       </c>
-      <c r="I181">
+      <c r="I181" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5697,148 +5704,148 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A183">
-        <v>1</v>
-      </c>
-      <c r="B183">
+    <row r="183" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="2">
+        <v>1</v>
+      </c>
+      <c r="B183" s="2">
         <v>111</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="2">
         <v>86</v>
       </c>
-      <c r="D183">
+      <c r="D183" s="2">
         <v>19</v>
       </c>
-      <c r="E183">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F183">
+      <c r="E183" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F183" s="2">
         <v>30.1</v>
       </c>
-      <c r="G183">
+      <c r="G183" s="2">
         <v>0.14299999999999999</v>
       </c>
-      <c r="H183">
+      <c r="H183" s="2">
         <v>23</v>
       </c>
-      <c r="I183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A184">
+      <c r="I183" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="2">
         <v>2</v>
       </c>
-      <c r="B184">
+      <c r="B184" s="2">
         <v>129</v>
       </c>
-      <c r="C184">
+      <c r="C184" s="2">
         <v>84</v>
       </c>
-      <c r="D184">
-        <v>20.536458333333329</v>
-      </c>
-      <c r="E184">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F184">
+      <c r="D184" s="2">
+        <v>20.536458333333329</v>
+      </c>
+      <c r="E184" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F184" s="2">
         <v>28</v>
       </c>
-      <c r="G184">
+      <c r="G184" s="2">
         <v>0.28399999999999997</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="2">
         <v>27</v>
       </c>
-      <c r="I184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A185">
+      <c r="I184" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="2">
         <v>2</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="2">
         <v>90</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="2">
         <v>80</v>
       </c>
-      <c r="D185">
+      <c r="D185" s="2">
         <v>14</v>
       </c>
-      <c r="E185">
+      <c r="E185" s="2">
         <v>55</v>
       </c>
-      <c r="F185">
+      <c r="F185" s="2">
         <v>24.4</v>
       </c>
-      <c r="G185">
+      <c r="G185" s="2">
         <v>0.249</v>
       </c>
-      <c r="H185">
+      <c r="H185" s="2">
         <v>24</v>
       </c>
-      <c r="I185">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A186">
-        <v>0</v>
-      </c>
-      <c r="B186">
+      <c r="I185" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="2">
+        <v>0</v>
+      </c>
+      <c r="B186" s="2">
         <v>86</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="2">
         <v>68</v>
       </c>
-      <c r="D186">
+      <c r="D186" s="2">
         <v>32</v>
       </c>
-      <c r="E186">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F186">
+      <c r="E186" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F186" s="2">
         <v>35.799999999999997</v>
       </c>
-      <c r="G186">
+      <c r="G186" s="2">
         <v>0.23799999999999999</v>
       </c>
-      <c r="H186">
+      <c r="H186" s="2">
         <v>25</v>
       </c>
-      <c r="I186">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A187">
-        <v>1</v>
-      </c>
-      <c r="B187">
+      <c r="I186" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="2">
+        <v>1</v>
+      </c>
+      <c r="B187" s="2">
         <v>113</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="2">
         <v>64</v>
       </c>
-      <c r="D187">
+      <c r="D187" s="2">
         <v>35</v>
       </c>
-      <c r="E187">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F187">
+      <c r="E187" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F187" s="2">
         <v>33.6</v>
       </c>
-      <c r="G187">
+      <c r="G187" s="2">
         <v>0.54300000000000004</v>
       </c>
-      <c r="H187">
+      <c r="H187" s="2">
         <v>21</v>
       </c>
-      <c r="I187">
+      <c r="I187" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5871,32 +5878,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A189">
+    <row r="189" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="2">
         <v>3</v>
       </c>
-      <c r="B189">
+      <c r="B189" s="2">
         <v>191</v>
       </c>
-      <c r="C189">
+      <c r="C189" s="2">
         <v>68</v>
       </c>
-      <c r="D189">
+      <c r="D189" s="2">
         <v>15</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="2">
         <v>130</v>
       </c>
-      <c r="F189">
+      <c r="F189" s="2">
         <v>30.9</v>
       </c>
-      <c r="G189">
+      <c r="G189" s="2">
         <v>0.29899999999999999</v>
       </c>
-      <c r="H189">
+      <c r="H189" s="2">
         <v>34</v>
       </c>
-      <c r="I189">
+      <c r="I189" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6045,61 +6052,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A195">
-        <v>0</v>
-      </c>
-      <c r="B195">
+    <row r="195" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="2">
+        <v>0</v>
+      </c>
+      <c r="B195" s="2">
         <v>138</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="2">
         <v>69.10546875</v>
       </c>
-      <c r="D195">
-        <v>20.536458333333329</v>
-      </c>
-      <c r="E195">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F195">
+      <c r="D195" s="2">
+        <v>20.536458333333329</v>
+      </c>
+      <c r="E195" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F195" s="2">
         <v>36.299999999999997</v>
       </c>
-      <c r="G195">
+      <c r="G195" s="2">
         <v>0.93300000000000005</v>
       </c>
-      <c r="H195">
+      <c r="H195" s="2">
         <v>25</v>
       </c>
-      <c r="I195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A196">
+      <c r="I195" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="2">
         <v>2</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="2">
         <v>128</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="2">
         <v>64</v>
       </c>
-      <c r="D196">
+      <c r="D196" s="2">
         <v>42</v>
       </c>
-      <c r="E196">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F196">
+      <c r="E196" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F196" s="2">
         <v>40</v>
       </c>
-      <c r="G196">
+      <c r="G196" s="2">
         <v>1.101</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="2">
         <v>24</v>
       </c>
-      <c r="I196">
+      <c r="I196" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6219,32 +6226,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A201">
-        <v>1</v>
-      </c>
-      <c r="B201">
+    <row r="201" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="2">
+        <v>1</v>
+      </c>
+      <c r="B201" s="2">
         <v>71</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="2">
         <v>78</v>
       </c>
-      <c r="D201">
+      <c r="D201" s="2">
         <v>50</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="2">
         <v>45</v>
       </c>
-      <c r="F201">
+      <c r="F201" s="2">
         <v>33.200000000000003</v>
       </c>
-      <c r="G201">
+      <c r="G201" s="2">
         <v>0.42199999999999999</v>
       </c>
-      <c r="H201">
+      <c r="H201" s="2">
         <v>21</v>
       </c>
-      <c r="I201">
+      <c r="I201" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6335,32 +6342,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A205">
-        <v>0</v>
-      </c>
-      <c r="B205">
+    <row r="205" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="2">
+        <v>0</v>
+      </c>
+      <c r="B205" s="2">
         <v>104</v>
       </c>
-      <c r="C205">
+      <c r="C205" s="2">
         <v>64</v>
       </c>
-      <c r="D205">
+      <c r="D205" s="2">
         <v>23</v>
       </c>
-      <c r="E205">
+      <c r="E205" s="2">
         <v>116</v>
       </c>
-      <c r="F205">
+      <c r="F205" s="2">
         <v>27.8</v>
       </c>
-      <c r="G205">
+      <c r="G205" s="2">
         <v>0.45400000000000001</v>
       </c>
-      <c r="H205">
+      <c r="H205" s="2">
         <v>23</v>
       </c>
-      <c r="I205">
+      <c r="I205" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6393,32 +6400,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A207">
-        <v>0</v>
-      </c>
-      <c r="B207">
+    <row r="207" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="2">
+        <v>0</v>
+      </c>
+      <c r="B207" s="2">
         <v>146</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="2">
         <v>70</v>
       </c>
-      <c r="D207">
-        <v>20.536458333333329</v>
-      </c>
-      <c r="E207">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F207">
+      <c r="D207" s="2">
+        <v>20.536458333333329</v>
+      </c>
+      <c r="E207" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F207" s="2">
         <v>37.9</v>
       </c>
-      <c r="G207">
+      <c r="G207" s="2">
         <v>0.33400000000000002</v>
       </c>
-      <c r="H207">
+      <c r="H207" s="2">
         <v>28</v>
       </c>
-      <c r="I207">
+      <c r="I207" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6596,61 +6603,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A214">
-        <v>0</v>
-      </c>
-      <c r="B214">
+    <row r="214" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="2">
+        <v>0</v>
+      </c>
+      <c r="B214" s="2">
         <v>78</v>
       </c>
-      <c r="C214">
+      <c r="C214" s="2">
         <v>88</v>
       </c>
-      <c r="D214">
+      <c r="D214" s="2">
         <v>29</v>
       </c>
-      <c r="E214">
+      <c r="E214" s="2">
         <v>40</v>
       </c>
-      <c r="F214">
+      <c r="F214" s="2">
         <v>36.9</v>
       </c>
-      <c r="G214">
+      <c r="G214" s="2">
         <v>0.434</v>
       </c>
-      <c r="H214">
+      <c r="H214" s="2">
         <v>21</v>
       </c>
-      <c r="I214">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A215">
-        <v>0</v>
-      </c>
-      <c r="B215">
+      <c r="I214" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="2">
+        <v>0</v>
+      </c>
+      <c r="B215" s="2">
         <v>107</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="2">
         <v>62</v>
       </c>
-      <c r="D215">
+      <c r="D215" s="2">
         <v>30</v>
       </c>
-      <c r="E215">
+      <c r="E215" s="2">
         <v>74</v>
       </c>
-      <c r="F215">
+      <c r="F215" s="2">
         <v>36.6</v>
       </c>
-      <c r="G215">
+      <c r="G215" s="2">
         <v>0.75700000000000001</v>
       </c>
-      <c r="H215">
+      <c r="H215" s="2">
         <v>25</v>
       </c>
-      <c r="I215">
+      <c r="I215" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6770,32 +6777,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A220">
-        <v>0</v>
-      </c>
-      <c r="B220">
+    <row r="220" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="2">
+        <v>0</v>
+      </c>
+      <c r="B220" s="2">
         <v>167</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="2">
         <v>69.10546875</v>
       </c>
-      <c r="D220">
-        <v>20.536458333333329</v>
-      </c>
-      <c r="E220">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F220">
+      <c r="D220" s="2">
+        <v>20.536458333333329</v>
+      </c>
+      <c r="E220" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F220" s="2">
         <v>32.299999999999997</v>
       </c>
-      <c r="G220">
+      <c r="G220" s="2">
         <v>0.83899999999999997</v>
       </c>
-      <c r="H220">
+      <c r="H220" s="2">
         <v>30</v>
       </c>
-      <c r="I220">
+      <c r="I220" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6944,61 +6951,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A226">
-        <v>0</v>
-      </c>
-      <c r="B226">
+    <row r="226" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="2">
+        <v>0</v>
+      </c>
+      <c r="B226" s="2">
         <v>137</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="2">
         <v>68</v>
       </c>
-      <c r="D226">
+      <c r="D226" s="2">
         <v>14</v>
       </c>
-      <c r="E226">
+      <c r="E226" s="2">
         <v>148</v>
       </c>
-      <c r="F226">
+      <c r="F226" s="2">
         <v>24.8</v>
       </c>
-      <c r="G226">
+      <c r="G226" s="2">
         <v>0.14299999999999999</v>
       </c>
-      <c r="H226">
+      <c r="H226" s="2">
         <v>21</v>
       </c>
-      <c r="I226">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A227">
-        <v>0</v>
-      </c>
-      <c r="B227">
+      <c r="I226" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="2">
+        <v>0</v>
+      </c>
+      <c r="B227" s="2">
         <v>128</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="2">
         <v>68</v>
       </c>
-      <c r="D227">
+      <c r="D227" s="2">
         <v>19</v>
       </c>
-      <c r="E227">
+      <c r="E227" s="2">
         <v>180</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="2">
         <v>30.5</v>
       </c>
-      <c r="G227">
+      <c r="G227" s="2">
         <v>1.391</v>
       </c>
-      <c r="H227">
+      <c r="H227" s="2">
         <v>25</v>
       </c>
-      <c r="I227">
+      <c r="I227" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7031,61 +7038,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A229">
-        <v>0</v>
-      </c>
-      <c r="B229">
+    <row r="229" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="2">
+        <v>0</v>
+      </c>
+      <c r="B229" s="2">
         <v>106</v>
       </c>
-      <c r="C229">
+      <c r="C229" s="2">
         <v>70</v>
       </c>
-      <c r="D229">
+      <c r="D229" s="2">
         <v>37</v>
       </c>
-      <c r="E229">
+      <c r="E229" s="2">
         <v>148</v>
       </c>
-      <c r="F229">
+      <c r="F229" s="2">
         <v>39.4</v>
       </c>
-      <c r="G229">
+      <c r="G229" s="2">
         <v>0.60499999999999998</v>
       </c>
-      <c r="H229">
+      <c r="H229" s="2">
         <v>22</v>
       </c>
-      <c r="I229">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A230">
+      <c r="I229" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="2">
         <v>2</v>
       </c>
-      <c r="B230">
+      <c r="B230" s="2">
         <v>155</v>
       </c>
-      <c r="C230">
+      <c r="C230" s="2">
         <v>74</v>
       </c>
-      <c r="D230">
+      <c r="D230" s="2">
         <v>17</v>
       </c>
-      <c r="E230">
+      <c r="E230" s="2">
         <v>96</v>
       </c>
-      <c r="F230">
+      <c r="F230" s="2">
         <v>26.6</v>
       </c>
-      <c r="G230">
+      <c r="G230" s="2">
         <v>0.433</v>
       </c>
-      <c r="H230">
+      <c r="H230" s="2">
         <v>27</v>
       </c>
-      <c r="I230">
+      <c r="I230" s="2">
         <v>1</v>
       </c>
     </row>
@@ -7118,61 +7125,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A232">
+    <row r="232" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="2">
         <v>2</v>
       </c>
-      <c r="B232">
+      <c r="B232" s="2">
         <v>112</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="2">
         <v>68</v>
       </c>
-      <c r="D232">
+      <c r="D232" s="2">
         <v>22</v>
       </c>
-      <c r="E232">
+      <c r="E232" s="2">
         <v>94</v>
       </c>
-      <c r="F232">
+      <c r="F232" s="2">
         <v>34.1</v>
       </c>
-      <c r="G232">
+      <c r="G232" s="2">
         <v>0.315</v>
       </c>
-      <c r="H232">
+      <c r="H232" s="2">
         <v>26</v>
       </c>
-      <c r="I232">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A233">
+      <c r="I232" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="2">
         <v>3</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="2">
         <v>99</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="2">
         <v>80</v>
       </c>
-      <c r="D233">
+      <c r="D233" s="2">
         <v>11</v>
       </c>
-      <c r="E233">
+      <c r="E233" s="2">
         <v>64</v>
       </c>
-      <c r="F233">
+      <c r="F233" s="2">
         <v>19.3</v>
       </c>
-      <c r="G233">
+      <c r="G233" s="2">
         <v>0.28399999999999997</v>
       </c>
-      <c r="H233">
+      <c r="H233" s="2">
         <v>30</v>
       </c>
-      <c r="I233">
+      <c r="I233" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7292,61 +7299,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A238">
-        <v>0</v>
-      </c>
-      <c r="B238">
+    <row r="238" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="2">
+        <v>0</v>
+      </c>
+      <c r="B238" s="2">
         <v>124</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="2">
         <v>70</v>
       </c>
-      <c r="D238">
+      <c r="D238" s="2">
         <v>20</v>
       </c>
-      <c r="E238">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F238">
+      <c r="E238" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F238" s="2">
         <v>27.4</v>
       </c>
-      <c r="G238">
+      <c r="G238" s="2">
         <v>0.254</v>
       </c>
-      <c r="H238">
+      <c r="H238" s="2">
         <v>36</v>
       </c>
-      <c r="I238">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A239">
+      <c r="I238" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="2">
         <v>2</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="2">
         <v>112</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="2">
         <v>75</v>
       </c>
-      <c r="D239">
+      <c r="D239" s="2">
         <v>32</v>
       </c>
-      <c r="E239">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F239">
+      <c r="E239" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F239" s="2">
         <v>35.700000000000003</v>
       </c>
-      <c r="G239">
+      <c r="G239" s="2">
         <v>0.14799999999999999</v>
       </c>
-      <c r="H239">
+      <c r="H239" s="2">
         <v>21</v>
       </c>
-      <c r="I239">
+      <c r="I239" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7611,32 +7618,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A249">
-        <v>0</v>
-      </c>
-      <c r="B249">
+    <row r="249" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="3">
+        <v>0</v>
+      </c>
+      <c r="B249" s="3">
         <v>117</v>
       </c>
-      <c r="C249">
+      <c r="C249" s="3">
         <v>69.10546875</v>
       </c>
-      <c r="D249">
-        <v>20.536458333333329</v>
-      </c>
-      <c r="E249">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F249">
+      <c r="D249" s="3">
+        <v>20.536458333333329</v>
+      </c>
+      <c r="E249" s="3">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F249" s="3">
         <v>33.799999999999997</v>
       </c>
-      <c r="G249">
+      <c r="G249" s="3">
         <v>0.93200000000000005</v>
       </c>
-      <c r="H249">
+      <c r="H249" s="3">
         <v>44</v>
       </c>
-      <c r="I249">
+      <c r="I249" s="3">
         <v>0</v>
       </c>
     </row>
@@ -8307,32 +8314,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A273">
-        <v>0</v>
-      </c>
-      <c r="B273">
+    <row r="273" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="2">
+        <v>0</v>
+      </c>
+      <c r="B273" s="2">
         <v>101</v>
       </c>
-      <c r="C273">
+      <c r="C273" s="2">
         <v>64</v>
       </c>
-      <c r="D273">
+      <c r="D273" s="2">
         <v>17</v>
       </c>
-      <c r="E273">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F273">
+      <c r="E273" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F273" s="2">
         <v>21</v>
       </c>
-      <c r="G273">
+      <c r="G273" s="2">
         <v>0.252</v>
       </c>
-      <c r="H273">
+      <c r="H273" s="2">
         <v>21</v>
       </c>
-      <c r="I273">
+      <c r="I273" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8365,119 +8372,119 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A275">
-        <v>1</v>
-      </c>
-      <c r="B275">
+    <row r="275" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="2">
+        <v>1</v>
+      </c>
+      <c r="B275" s="2">
         <v>133</v>
       </c>
-      <c r="C275">
+      <c r="C275" s="2">
         <v>102</v>
       </c>
-      <c r="D275">
+      <c r="D275" s="2">
         <v>28</v>
       </c>
-      <c r="E275">
+      <c r="E275" s="2">
         <v>140</v>
       </c>
-      <c r="F275">
+      <c r="F275" s="2">
         <v>32.799999999999997</v>
       </c>
-      <c r="G275">
+      <c r="G275" s="2">
         <v>0.23400000000000001</v>
       </c>
-      <c r="H275">
+      <c r="H275" s="2">
         <v>45</v>
       </c>
-      <c r="I275">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A276">
-        <v>0</v>
-      </c>
-      <c r="B276">
+      <c r="I275" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="2">
+        <v>0</v>
+      </c>
+      <c r="B276" s="2">
         <v>118</v>
       </c>
-      <c r="C276">
+      <c r="C276" s="2">
         <v>64</v>
       </c>
-      <c r="D276">
+      <c r="D276" s="2">
         <v>23</v>
       </c>
-      <c r="E276">
+      <c r="E276" s="2">
         <v>89</v>
       </c>
-      <c r="F276">
+      <c r="F276" s="2">
         <v>31.992578125000001</v>
       </c>
-      <c r="G276">
+      <c r="G276" s="2">
         <v>1.7310000000000001</v>
       </c>
-      <c r="H276">
+      <c r="H276" s="2">
         <v>21</v>
       </c>
-      <c r="I276">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A277">
-        <v>0</v>
-      </c>
-      <c r="B277">
+      <c r="I276" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="2">
+        <v>0</v>
+      </c>
+      <c r="B277" s="2">
         <v>84</v>
       </c>
-      <c r="C277">
+      <c r="C277" s="2">
         <v>64</v>
       </c>
-      <c r="D277">
+      <c r="D277" s="2">
         <v>22</v>
       </c>
-      <c r="E277">
+      <c r="E277" s="2">
         <v>66</v>
       </c>
-      <c r="F277">
+      <c r="F277" s="2">
         <v>35.799999999999997</v>
       </c>
-      <c r="G277">
+      <c r="G277" s="2">
         <v>0.54500000000000004</v>
       </c>
-      <c r="H277">
+      <c r="H277" s="2">
         <v>21</v>
       </c>
-      <c r="I277">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A278">
-        <v>0</v>
-      </c>
-      <c r="B278">
+      <c r="I277" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="2">
+        <v>0</v>
+      </c>
+      <c r="B278" s="2">
         <v>98</v>
       </c>
-      <c r="C278">
+      <c r="C278" s="2">
         <v>82</v>
       </c>
-      <c r="D278">
+      <c r="D278" s="2">
         <v>15</v>
       </c>
-      <c r="E278">
+      <c r="E278" s="2">
         <v>84</v>
       </c>
-      <c r="F278">
+      <c r="F278" s="2">
         <v>25.2</v>
       </c>
-      <c r="G278">
+      <c r="G278" s="2">
         <v>0.29899999999999999</v>
       </c>
-      <c r="H278">
+      <c r="H278" s="2">
         <v>22</v>
       </c>
-      <c r="I278">
+      <c r="I278" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8539,32 +8546,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A281">
-        <v>0</v>
-      </c>
-      <c r="B281">
+    <row r="281" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="2">
+        <v>0</v>
+      </c>
+      <c r="B281" s="2">
         <v>93</v>
       </c>
-      <c r="C281">
+      <c r="C281" s="2">
         <v>100</v>
       </c>
-      <c r="D281">
+      <c r="D281" s="2">
         <v>39</v>
       </c>
-      <c r="E281">
+      <c r="E281" s="2">
         <v>72</v>
       </c>
-      <c r="F281">
+      <c r="F281" s="2">
         <v>43.4</v>
       </c>
-      <c r="G281">
+      <c r="G281" s="2">
         <v>1.0209999999999999</v>
       </c>
-      <c r="H281">
+      <c r="H281" s="2">
         <v>35</v>
       </c>
-      <c r="I281">
+      <c r="I281" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8597,90 +8604,90 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A283">
-        <v>0</v>
-      </c>
-      <c r="B283">
+    <row r="283" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="2">
+        <v>0</v>
+      </c>
+      <c r="B283" s="2">
         <v>105</v>
       </c>
-      <c r="C283">
+      <c r="C283" s="2">
         <v>68</v>
       </c>
-      <c r="D283">
+      <c r="D283" s="2">
         <v>22</v>
       </c>
-      <c r="E283">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F283">
+      <c r="E283" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F283" s="2">
         <v>20</v>
       </c>
-      <c r="G283">
+      <c r="G283" s="2">
         <v>0.23599999999999999</v>
       </c>
-      <c r="H283">
+      <c r="H283" s="2">
         <v>22</v>
       </c>
-      <c r="I283">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A284">
-        <v>1</v>
-      </c>
-      <c r="B284">
+      <c r="I283" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="2">
+        <v>1</v>
+      </c>
+      <c r="B284" s="2">
         <v>109</v>
       </c>
-      <c r="C284">
+      <c r="C284" s="2">
         <v>60</v>
       </c>
-      <c r="D284">
+      <c r="D284" s="2">
         <v>8</v>
       </c>
-      <c r="E284">
+      <c r="E284" s="2">
         <v>182</v>
       </c>
-      <c r="F284">
+      <c r="F284" s="2">
         <v>25.4</v>
       </c>
-      <c r="G284">
+      <c r="G284" s="2">
         <v>0.94699999999999995</v>
       </c>
-      <c r="H284">
+      <c r="H284" s="2">
         <v>21</v>
       </c>
-      <c r="I284">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A285">
-        <v>1</v>
-      </c>
-      <c r="B285">
+      <c r="I284" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="2">
+        <v>1</v>
+      </c>
+      <c r="B285" s="2">
         <v>90</v>
       </c>
-      <c r="C285">
+      <c r="C285" s="2">
         <v>62</v>
       </c>
-      <c r="D285">
+      <c r="D285" s="2">
         <v>18</v>
       </c>
-      <c r="E285">
+      <c r="E285" s="2">
         <v>59</v>
       </c>
-      <c r="F285">
+      <c r="F285" s="2">
         <v>25.1</v>
       </c>
-      <c r="G285">
+      <c r="G285" s="2">
         <v>1.268</v>
       </c>
-      <c r="H285">
+      <c r="H285" s="2">
         <v>25</v>
       </c>
-      <c r="I285">
+      <c r="I285" s="2">
         <v>0</v>
       </c>
     </row>
@@ -8916,32 +8923,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A294">
-        <v>0</v>
-      </c>
-      <c r="B294">
+    <row r="294" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="2">
+        <v>0</v>
+      </c>
+      <c r="B294" s="2">
         <v>131</v>
       </c>
-      <c r="C294">
+      <c r="C294" s="2">
         <v>66</v>
       </c>
-      <c r="D294">
+      <c r="D294" s="2">
         <v>40</v>
       </c>
-      <c r="E294">
-        <v>79.799479166666671</v>
-      </c>
-      <c r="F294">
+      <c r="E294" s="2">
+        <v>79.799479166666671</v>
+      </c>
+      <c r="F294" s="2">
         <v>34.299999999999997</v>
       </c>
-      <c r="G294">
+      <c r="G294" s="2">
         <v>0.19600000000000001</v>
       </c>
-      <c r="H294">
+      <c r="H294" s="2">
         <v>22</v>
       </c>
-      <c r="I294">
+      <c r="I294" s="2">
         <v>1</v>
       </c>
     </row>
@@ -9264,32 +9271,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A306">
-        <v>1</v>
-      </c>
-      <c r="B306">
+    <row r="306" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="2">
+        <v>1</v>
+      </c>
+      <c r="B306" s="2">
         <v>112</v>
       </c>
-      <c r="C306">
+      <c r="C306" s="2">
         <v>72</v>
       </c>
-      <c r="D306">
+      <c r="D306" s="2">
         <v>30</v>
       </c>
-      <c r="E306">
+      <c r="E306" s="2">
         <v>176</v>
       </c>
-      <c r="F306">
+      <c r="F306" s="2">
         <v>34.4</v>
       </c>
-      <c r="G306">
+      <c r="G306" s="2">
         <v>0.52800000000000002</v>
       </c>
-      <c r="H306">
+      <c r="H306" s="2">
         <v>25</v>
       </c>
-      <c r="I306">
+      <c r="I306" s="2">
         <v>0</v>
       </c>
     </row>
@@ -9322,32 +9329,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A308">
-        <v>0</v>
-      </c>
-      <c r="B308">
+    <row r="308" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="2">
+        <v>0</v>
+      </c>
+      <c r="B308" s="2">
         <v>138</v>
       </c>
-      <c r="C308">
+      <c r="C308" s="2">
         <v>60</v>
       </c>
-      <c r="D308">
+      <c r="D308" s="2">
         <v>35</v>
       </c>
-      <c r="E308">
+      <c r="E308" s="2">
         <v>167</v>
       </c>
-      <c r="F308">
+      <c r="F308" s="2">
         <v>34.6</v>
       </c>
-      <c r="G308">
+      <c r="G308" s="2">
         <v>0.53400000000000003</v>
       </c>
-      <c r="H308">
+      <c r="H308" s="2">
         <v>21</v>
       </c>
-      <c r="I308">
+      <c r="I308" s="2">
         <v>1</v>
       </c>
     </row>
@@ -9467,32 +9474,32 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A313">
-        <v>1</v>
-      </c>
-      <c r="B313">
+    <row r="313" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A313" s="2">
+        <v>1</v>
+      </c>
+      <c r="B313" s="2">
         <v>119</v>
       </c>
-      <c r="C313">
+      <c r="C313" s="2">
         <v>88</v>
       </c>
-      <c r="D313">
+      <c r="D313" s="2">
         <v>41</v>
       </c>
-      <c r="E313">
+      <c r="E313" s="2">
         <v>170</v>
       </c>
-      <c r="F313">
+      <c r="F313" s="2">
         <v>45.3</v>
       </c>
-      <c r="G313">
+      <c r="G313" s="2">
         <v>0.50700000000000001</v>
       </c>
-      <c r="H313">
+      <c r="H313" s="2">
         <v>26</v>
       </c>
-      <c r="I313">
+      <c r="I313" s="2">
         <v>0</v>
       </c>
     </row>
